--- a/experiment/Omni+CNN_2CH_bestx4/Test/results-Urban100/Urban100.xlsx
+++ b/experiment/Omni+CNN_2CH_bestx4/Test/results-Urban100/Urban100.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27.66</v>
+        <v>27.69</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7693</v>
+        <v>0.7713</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.73</v>
+        <v>26.81</v>
       </c>
       <c r="C3" t="n">
-        <v>0.819</v>
+        <v>0.8222</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.92</v>
+        <v>23.98</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6902</v>
+        <v>0.6945</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.52</v>
+        <v>23.51</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8411</v>
+        <v>0.8397</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28.24</v>
+        <v>28.25</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9523</v>
+        <v>0.9515</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22.56</v>
+        <v>22.63</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6298</v>
+        <v>0.6332</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29.67</v>
+        <v>29.73</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8643</v>
+        <v>0.8648</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21.57</v>
+        <v>21.62</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6681</v>
+        <v>0.6725</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>33.87</v>
+        <v>33.93</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9288999999999999</v>
+        <v>0.9278999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27.39</v>
+        <v>27.2</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8905999999999999</v>
+        <v>0.8871</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18.1</v>
+        <v>18.12</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7907</v>
+        <v>0.7945</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24.02</v>
+        <v>23.99</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7415</v>
+        <v>0.7407</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29.69</v>
+        <v>29.68</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8427</v>
+        <v>0.8424</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22.47</v>
+        <v>22.44</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6924</v>
+        <v>0.6941000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>26.24</v>
+        <v>26.27</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7393999999999999</v>
+        <v>0.7403999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30.41</v>
+        <v>30.52</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9156</v>
+        <v>0.9165</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25.88</v>
+        <v>25.85</v>
       </c>
       <c r="C18" t="n">
-        <v>0.832</v>
+        <v>0.8312</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>26.39</v>
+        <v>26.4</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7169</v>
+        <v>0.7173</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>22.28</v>
+        <v>22.34</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8191000000000001</v>
+        <v>0.8226</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22.22</v>
+        <v>22.2</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7242</v>
+        <v>0.7254</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>29.81</v>
+        <v>29.78</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7867</v>
+        <v>0.7863</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>26.12</v>
+        <v>26.14</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7621</v>
+        <v>0.7627</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>30.48</v>
+        <v>30.78</v>
       </c>
       <c r="C24" t="n">
-        <v>0.915</v>
+        <v>0.9205</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>20.43</v>
+        <v>20.34</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6699000000000001</v>
+        <v>0.6679</v>
       </c>
     </row>
     <row r="26">
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32.22</v>
+        <v>32.04</v>
       </c>
       <c r="C26" t="n">
         <v>0.9026999999999999</v>
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27.99</v>
+        <v>27.89</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7068</v>
+        <v>0.7060999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28.39</v>
+        <v>28.5</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7982</v>
+        <v>0.8025</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>31.54</v>
+        <v>31.59</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8782</v>
+        <v>0.8788</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>26.98</v>
+        <v>27.05</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8669</v>
+        <v>0.8679</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>24.92</v>
+        <v>24.82</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8216</v>
+        <v>0.8186</v>
       </c>
     </row>
     <row r="32">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>24.33</v>
+        <v>24.31</v>
       </c>
       <c r="C32" t="n">
         <v>0.7956</v>
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29.28</v>
+        <v>29.07</v>
       </c>
       <c r="C33" t="n">
-        <v>0.858</v>
+        <v>0.8539</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>27.38</v>
+        <v>27.4</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8119</v>
+        <v>0.8097</v>
       </c>
     </row>
     <row r="35">
@@ -884,7 +884,7 @@
         <v>23.18</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5907</v>
+        <v>0.5911</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29.34</v>
+        <v>29.31</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8808</v>
+        <v>0.8794999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>28.88</v>
+        <v>29.04</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8874</v>
+        <v>0.8894</v>
       </c>
     </row>
     <row r="38">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>26.56</v>
+        <v>26.57</v>
       </c>
       <c r="C38" t="n">
         <v>0.8033</v>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>27.18</v>
+        <v>27.23</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6919999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>23.1</v>
+        <v>23.17</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7512</v>
+        <v>0.7532</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>27.05</v>
+        <v>26.67</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9403</v>
+        <v>0.9361</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26.73</v>
+        <v>26.68</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8871</v>
+        <v>0.8878</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>28.96</v>
+        <v>28.9</v>
       </c>
       <c r="C43" t="n">
-        <v>0.8887</v>
+        <v>0.8875</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>32.13</v>
+        <v>31.68</v>
       </c>
       <c r="C44" t="n">
-        <v>0.9333</v>
+        <v>0.9327</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>31.94</v>
+        <v>31.88</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8703</v>
+        <v>0.8692</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>23.85</v>
+        <v>24.09</v>
       </c>
       <c r="C46" t="n">
-        <v>0.7085</v>
+        <v>0.7206</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>23.7</v>
+        <v>23.75</v>
       </c>
       <c r="C47" t="n">
-        <v>0.762</v>
+        <v>0.7645</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>22.1</v>
+        <v>22.12</v>
       </c>
       <c r="C48" t="n">
-        <v>0.778</v>
+        <v>0.7825</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>20.72</v>
+        <v>20.66</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8282</v>
+        <v>0.8287</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>23.59</v>
+        <v>23.62</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7547</v>
+        <v>0.7558</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25.34</v>
+        <v>25.4</v>
       </c>
       <c r="C51" t="n">
-        <v>0.7739</v>
+        <v>0.7772</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>27.58</v>
+        <v>27.52</v>
       </c>
       <c r="C52" t="n">
-        <v>0.8534</v>
+        <v>0.8529</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>28.97</v>
+        <v>28.98</v>
       </c>
       <c r="C53" t="n">
-        <v>0.9086</v>
+        <v>0.9079</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>22.47</v>
+        <v>22.49</v>
       </c>
       <c r="C54" t="n">
-        <v>0.7331</v>
+        <v>0.7344000000000001</v>
       </c>
     </row>
     <row r="55">
@@ -1144,7 +1144,7 @@
         <v>21.3</v>
       </c>
       <c r="C55" t="n">
-        <v>0.6562</v>
+        <v>0.6577</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>33.19</v>
+        <v>33.41</v>
       </c>
       <c r="C56" t="n">
-        <v>0.9461000000000001</v>
+        <v>0.9455</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25.17</v>
+        <v>25.18</v>
       </c>
       <c r="C57" t="n">
-        <v>0.7895</v>
+        <v>0.7907</v>
       </c>
     </row>
     <row r="58">
@@ -1183,7 +1183,7 @@
         <v>31.06</v>
       </c>
       <c r="C58" t="n">
-        <v>0.8987000000000001</v>
+        <v>0.8998</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>26.05</v>
+        <v>26.1</v>
       </c>
       <c r="C59" t="n">
-        <v>0.864</v>
+        <v>0.8665</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>22.29</v>
+        <v>22.33</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7688</v>
+        <v>0.7715</v>
       </c>
     </row>
     <row r="61">
@@ -1222,7 +1222,7 @@
         <v>22.62</v>
       </c>
       <c r="C61" t="n">
-        <v>0.5715</v>
+        <v>0.5739</v>
       </c>
     </row>
     <row r="62">
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>24.83</v>
+        <v>24.8</v>
       </c>
       <c r="C62" t="n">
         <v>0.7634</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>21.89</v>
+        <v>22.02</v>
       </c>
       <c r="C63" t="n">
-        <v>0.8172</v>
+        <v>0.8239</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>22.46</v>
+        <v>22.5</v>
       </c>
       <c r="C64" t="n">
-        <v>0.6208</v>
+        <v>0.623</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>26.73</v>
+        <v>26.7</v>
       </c>
       <c r="C65" t="n">
-        <v>0.7889</v>
+        <v>0.7894</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>25.51</v>
+        <v>25.53</v>
       </c>
       <c r="C66" t="n">
-        <v>0.7292999999999999</v>
+        <v>0.7315</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>22.27</v>
+        <v>22.29</v>
       </c>
       <c r="C67" t="n">
-        <v>0.6461</v>
+        <v>0.6492</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>20.22</v>
+        <v>20.27</v>
       </c>
       <c r="C68" t="n">
-        <v>0.8829</v>
+        <v>0.8853</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>30.65</v>
+        <v>30.61</v>
       </c>
       <c r="C69" t="n">
-        <v>0.8888</v>
+        <v>0.8907</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>24.86</v>
+        <v>24.89</v>
       </c>
       <c r="C70" t="n">
-        <v>0.7569</v>
+        <v>0.7581</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>22.15</v>
+        <v>22.18</v>
       </c>
       <c r="C71" t="n">
-        <v>0.5985</v>
+        <v>0.5996</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>28.14</v>
+        <v>28.11</v>
       </c>
       <c r="C72" t="n">
-        <v>0.6711</v>
+        <v>0.6709000000000001</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>20.32</v>
+        <v>20.48</v>
       </c>
       <c r="C73" t="n">
-        <v>0.8238</v>
+        <v>0.8300999999999999</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>19.89</v>
+        <v>20.21</v>
       </c>
       <c r="C74" t="n">
-        <v>0.5691000000000001</v>
+        <v>0.5798</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>23.86</v>
+        <v>23.84</v>
       </c>
       <c r="C75" t="n">
-        <v>0.7174</v>
+        <v>0.7129</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>31.93</v>
+        <v>31.91</v>
       </c>
       <c r="C76" t="n">
-        <v>0.8885999999999999</v>
+        <v>0.8883</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>23.1</v>
+        <v>23.01</v>
       </c>
       <c r="C77" t="n">
-        <v>0.7405</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>22.74</v>
+        <v>22.76</v>
       </c>
       <c r="C78" t="n">
-        <v>0.6765</v>
+        <v>0.6778</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>27.32</v>
+        <v>27.3</v>
       </c>
       <c r="C79" t="n">
-        <v>0.7737000000000001</v>
+        <v>0.7758</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>25.56</v>
+        <v>25.55</v>
       </c>
       <c r="C80" t="n">
-        <v>0.7016</v>
+        <v>0.7015</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>35.75</v>
+        <v>35.67</v>
       </c>
       <c r="C81" t="n">
-        <v>0.9535</v>
+        <v>0.9538</v>
       </c>
     </row>
     <row r="82">
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>37.4</v>
+        <v>37.15</v>
       </c>
       <c r="C82" t="n">
         <v>0.9699</v>
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>32.84</v>
+        <v>32.74</v>
       </c>
       <c r="C83" t="n">
-        <v>0.9413</v>
+        <v>0.9404</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>22.32</v>
+        <v>22.31</v>
       </c>
       <c r="C84" t="n">
-        <v>0.7017</v>
+        <v>0.7055</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>28.77</v>
+        <v>28.8</v>
       </c>
       <c r="C85" t="n">
-        <v>0.8142</v>
+        <v>0.8154</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>28.37</v>
+        <v>28.51</v>
       </c>
       <c r="C86" t="n">
-        <v>0.9043</v>
+        <v>0.9055</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>30.48</v>
+        <v>30.63</v>
       </c>
       <c r="C87" t="n">
-        <v>0.8872</v>
+        <v>0.8885</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>27.99</v>
+        <v>27.97</v>
       </c>
       <c r="C88" t="n">
-        <v>0.8892</v>
+        <v>0.8897</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>19.95</v>
+        <v>19.91</v>
       </c>
       <c r="C89" t="n">
-        <v>0.5772</v>
+        <v>0.5770999999999999</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>26.82</v>
+        <v>26.8</v>
       </c>
       <c r="C90" t="n">
-        <v>0.7192</v>
+        <v>0.7195</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>38.2</v>
+        <v>38.39</v>
       </c>
       <c r="C91" t="n">
-        <v>0.9758</v>
+        <v>0.9765</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>24.06</v>
+        <v>24.04</v>
       </c>
       <c r="C92" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.6861</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>19</v>
+        <v>18.93</v>
       </c>
       <c r="C93" t="n">
-        <v>0.6587</v>
+        <v>0.6582</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>28.46</v>
+        <v>28.42</v>
       </c>
       <c r="C94" t="n">
-        <v>0.9209000000000001</v>
+        <v>0.9212</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>27.2</v>
+        <v>27.25</v>
       </c>
       <c r="C95" t="n">
-        <v>0.7855</v>
+        <v>0.7866</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>20.21</v>
+        <v>20.1</v>
       </c>
       <c r="C96" t="n">
-        <v>0.4529</v>
+        <v>0.4498</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>25.8</v>
+        <v>25.58</v>
       </c>
       <c r="C97" t="n">
-        <v>0.8777</v>
+        <v>0.8746</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>25.01</v>
+        <v>25.05</v>
       </c>
       <c r="C98" t="n">
-        <v>0.7675</v>
+        <v>0.7691</v>
       </c>
     </row>
     <row r="99">
@@ -1716,7 +1716,7 @@
         <v>20.77</v>
       </c>
       <c r="C99" t="n">
-        <v>0.5371</v>
+        <v>0.5407999999999999</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>26.22</v>
+        <v>26.04</v>
       </c>
       <c r="C100" t="n">
-        <v>0.8076</v>
+        <v>0.8074</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>26.32</v>
+        <v>26.27</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7504999999999999</v>
+        <v>0.7485000000000001</v>
       </c>
     </row>
     <row r="102">
@@ -1755,7 +1755,7 @@
         <v>26.14</v>
       </c>
       <c r="C102" t="n">
-        <v>0.7879</v>
+        <v>0.7889</v>
       </c>
     </row>
   </sheetData>
